--- a/backend/backups/category14_moving_delivery_local_assistance_FINAL.xlsx
+++ b/backend/backups/category14_moving_delivery_local_assistance_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,415 +425,448 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>142ef794-67df-55ce-aefe-17722c4ba8bd</t>
+          <t>1c01b197-30f4-5d69-8c3a-a0be63889195</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Service Variation 1</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Delivery &amp; Pickup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing</t>
+          <t>Express Intra-City Document &amp; Parcel Pickup</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1400</v>
+        <v>249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Immediate two-wheeler courier picking up urgent business files, keys, or gifts.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Express Intra-City Document &amp; Parcel Pickup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable home shifting &amp; packing services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Home Shifting &amp; Packing professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Express Intra-City Document &amp; Parcel Pickup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.153348+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.153348+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Express Intra-City Document &amp; Parcel Pickup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bf9ef6d3-0143-5c64-9c1f-8463308554b7</t>
+          <t>43feb320-ba7d-5f6e-b659-a4e33877a25c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Service Variation 2</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Delivery &amp; Pickup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing</t>
+          <t>Heavy Luggage &amp; Suitcase Airport Transport</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1800</v>
+        <v>699</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Doorstep pickup of heavy excess baggage delivered directly to airport terminal or home.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Heavy Luggage &amp; Suitcase Airport Transport procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable home shifting &amp; packing services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Home Shifting &amp; Packing professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Heavy Luggage &amp; Suitcase Airport Transport procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.157103+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.157103+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Heavy Luggage &amp; Suitcase Airport Transport take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>44bc15d3-2dc2-5407-9a0e-a84a536cf53d</t>
+          <t>e216c0f0-cc0c-5dfb-ae9d-b71cc9ee5f06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Service Variation 3</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Home Shifting &amp; Packing</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing</t>
+          <t>Home Shifting &amp; Packing Premium Care Option 18</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2200</v>
+        <v>3799</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Home Shifting &amp; Packing service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Home Shifting &amp; Packing Premium Care Option 18 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable home shifting &amp; packing services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Home Shifting &amp; Packing professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Home Shifting &amp; Packing Premium Care Option 18 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.159486+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.159486+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Home Shifting &amp; Packing Premium Care Option 18 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e216c0f0-cc0c-5dfb-ae9d-b71cc9ee5f06</t>
+          <t>6dbabdc9-db64-5d81-bbdb-3e92e340fb58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Service Variation 4</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Home Shifting &amp; Packing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing</t>
+          <t>Home Shifting &amp; Packing Premium Care Option 3</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2600</v>
+        <v>2299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Home Shifting &amp; Packing service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Home Shifting &amp; Packing Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable home shifting &amp; packing services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Home Shifting &amp; Packing professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Home Shifting &amp; Packing Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.162194+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.162194+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Home Shifting &amp; Packing Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1c01b197-30f4-5d69-8c3a-a0be63889195</t>
+          <t>bf9ef6d3-0143-5c64-9c1f-8463308554b7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Service Variation 5</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Home Shifting &amp; Packing</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing</t>
+          <t>Home Shifting &amp; Packing Premium Care Option 9</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3000</v>
+        <v>2899</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Home Shifting &amp; Packing service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Home Shifting &amp; Packing Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable home shifting &amp; packing services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Home Shifting &amp; Packing professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Home Shifting &amp; Packing Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.164726+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.164726+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Home Shifting &amp; Packing Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6dbabdc9-db64-5d81-bbdb-3e92e340fb58</t>
+          <t>d40b03ca-14cc-5075-a4c5-c823dd823935</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Service Variation 6</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Junk Removal &amp; Disposal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing</t>
+          <t>Junk Removal &amp; Disposal Premium Care Option 14</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable home shifting &amp; packing services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Home Shifting &amp; Packing professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.166840+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.166840+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17f179bf-7667-5f3d-afd5-d4e4ee315620</t>
+          <t>7d11b486-1097-5341-a8a5-87ba0f75c18b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Service Variation 7</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Junk Removal &amp; Disposal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing</t>
+          <t>Junk Removal &amp; Disposal Premium Care Option 4</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3800</v>
+        <v>2399</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable home shifting &amp; packing services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Home Shifting &amp; Packing professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.169242+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.169242+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -862,895 +878,985 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Service Variation 1</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Junk Removal &amp; Disposal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal</t>
+          <t>Junk Removal &amp; Disposal Premium Care Option 5</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1400</v>
+        <v>2499</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable junk removal &amp; disposal services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Junk Removal &amp; Disposal professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.171289+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.171289+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ba26862d-85dd-5c2e-9ba0-78b615e06ad5</t>
+          <t>9d2e0a0b-cae2-5e9e-864b-e9c4084176e4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Service Variation 2</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Junk Removal &amp; Disposal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal</t>
+          <t>Junk Removal &amp; Disposal Premium Care Option 6</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1800</v>
+        <v>2599</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable junk removal &amp; disposal services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Junk Removal &amp; Disposal professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.173350+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.173350+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>d40b03ca-14cc-5075-a4c5-c823dd823935</t>
+          <t>ba26862d-85dd-5c2e-9ba0-78b615e06ad5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Service Variation 3</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Junk Removal &amp; Disposal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal</t>
+          <t>Junk Removal &amp; Disposal Premium Care Option 8</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2200</v>
+        <v>2799</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable junk removal &amp; disposal services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Junk Removal &amp; Disposal professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.175713+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.175713+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7d11b486-1097-5341-a8a5-87ba0f75c18b</t>
+          <t>bfc1a8a7-8d4f-5c7d-8866-6f33a9a90c3d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Service Variation 4</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Last-Mile Delivery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal</t>
+          <t>Last-Mile Delivery Premium Care Option 10</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2600</v>
+        <v>2999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Last-Mile Delivery service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Last-Mile Delivery Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable junk removal &amp; disposal services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Junk Removal &amp; Disposal professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Last-Mile Delivery Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.178704+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.178704+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Last-Mile Delivery Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9d2e0a0b-cae2-5e9e-864b-e9c4084176e4</t>
+          <t>c5096bf4-5677-50ed-bd66-23ab4e909013</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Service Variation 5</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Last-Mile Delivery</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal</t>
+          <t>Last-Mile Delivery Premium Care Option 11</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3000</v>
+        <v>3099</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Last-Mile Delivery service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Last-Mile Delivery Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable junk removal &amp; disposal services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Junk Removal &amp; Disposal professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Last-Mile Delivery Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.181482+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.181482+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Last-Mile Delivery Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>c5096bf4-5677-50ed-bd66-23ab4e909013</t>
+          <t>ce1ed4d8-259d-54ac-82a0-734b4fcbdc1b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Service Variation 1</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Last-Mile Delivery</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery</t>
+          <t>Last-Mile Delivery Premium Care Option 13</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1400</v>
+        <v>3299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Last-Mile Delivery service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Last-Mile Delivery Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable last-mile delivery services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Last-Mile Delivery professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Last-Mile Delivery Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.183687+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.183687+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Last-Mile Delivery Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bfc1a8a7-8d4f-5c7d-8866-6f33a9a90c3d</t>
+          <t>d569432a-b4cd-5584-9b6b-4a617ee57c03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Service Variation 2</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Last-Mile Delivery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery</t>
+          <t>Last-Mile Delivery Premium Care Option 15</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1800</v>
+        <v>3499</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Last-Mile Delivery service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Last-Mile Delivery Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable last-mile delivery services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Last-Mile Delivery professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Last-Mile Delivery Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.185828+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.185828+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Last-Mile Delivery Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1197b272-b994-5781-88a4-20fda966a48b</t>
+          <t>46d8db20-3e81-5240-8af7-c6aeb1680155</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Service Variation 3</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Local Errands &amp; Assistance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery</t>
+          <t>Local Errands &amp; Assistance Premium Care Option 1</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2200</v>
+        <v>2099</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Local Errands &amp; Assistance service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Local Errands &amp; Assistance Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable last-mile delivery services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Last-Mile Delivery professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Local Errands &amp; Assistance Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.188463+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.188463+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Local Errands &amp; Assistance Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>d569432a-b4cd-5584-9b6b-4a617ee57c03</t>
+          <t>d91c5724-7eb7-5f63-bb00-97461b843b2c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Service Variation 4</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Local Errands &amp; Assistance</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery</t>
+          <t>Local Errands &amp; Assistance Premium Care Option 17</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2600</v>
+        <v>3699</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Local Errands &amp; Assistance service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Local Errands &amp; Assistance Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable last-mile delivery services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Last-Mile Delivery professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Local Errands &amp; Assistance Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.190699+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.190699+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Local Errands &amp; Assistance Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ce1ed4d8-259d-54ac-82a0-734b4fcbdc1b</t>
+          <t>a698a0c1-edb5-5247-92b7-7afd5d00c0d7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Service Variation 5</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Local Errands &amp; Assistance</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery</t>
+          <t>Local Errands &amp; Assistance Premium Care Option 7</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3000</v>
+        <v>2699</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Local Errands &amp; Assistance service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Local Errands &amp; Assistance Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable last-mile delivery services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Last-Mile Delivery professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Local Errands &amp; Assistance Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.192953+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.192953+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Local Errands &amp; Assistance Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a698a0c1-edb5-5247-92b7-7afd5d00c0d7</t>
+          <t>1197b272-b994-5781-88a4-20fda966a48b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance Service Variation 1</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Moving Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance</t>
+          <t>1 BHK Local Home Shifting &amp; Packing</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1400</v>
+        <v>4999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Professional bubble-wrap packing, loading into closed truck, transport, and unloading.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional 1 BHK Local Home Shifting &amp; Packing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable local errands &amp; assistance services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Local Errands &amp; Assistance professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 1 BHK Local Home Shifting &amp; Packing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.196104+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.196104+00:00</t>
+          <t>[{'answer': 'The session typically takes around 240 minutes.', 'question': 'How long does 1 BHK Local Home Shifting &amp; Packing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2faaeb27-4399-56f4-985d-157dd649daa4</t>
+          <t>142ef794-67df-55ce-aefe-17722c4ba8bd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance Service Variation 2</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Moving Services</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance</t>
+          <t>2 BHK City Relocation Packers &amp; Movers</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1800</v>
+        <v>7999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Multi-layer corrugated cardboard box packing, furniture dismantle/reassemble, and safe transport.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional 2 BHK City Relocation Packers &amp; Movers procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable local errands &amp; assistance services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Local Errands &amp; Assistance professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 2 BHK City Relocation Packers &amp; Movers procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.198324+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.198324+00:00</t>
+          <t>[{'answer': 'The session typically takes around 360 minutes.', 'question': 'How long does 2 BHK City Relocation Packers &amp; Movers take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>43feb320-ba7d-5f6e-b659-a4e33877a25c</t>
+          <t>2faaeb27-4399-56f4-985d-157dd649daa4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance Service Variation 3</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Moving Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance</t>
+          <t>Office Furniture &amp; Desktop Relocation Shifting</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2200</v>
+        <v>9999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Systematic IT equipment packing, server rack moving, and office desk installation.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Office Furniture &amp; Desktop Relocation Shifting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable local errands &amp; assistance services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Local Errands &amp; Assistance professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Office Furniture &amp; Desktop Relocation Shifting procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.200944+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.200944+00:00</t>
+          <t>[{'answer': 'The session typically takes around 360 minutes.', 'question': 'How long does Office Furniture &amp; Desktop Relocation Shifting take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>46d8db20-3e81-5240-8af7-c6aeb1680155</t>
+          <t>17f179bf-7667-5f3d-afd5-d4e4ee315620</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance Service Variation 4</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Moving Services</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance</t>
+          <t>Single Furniture Item Transport (Sofa / Bed / Fridge)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2600</v>
+        <v>1299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Tata Ace / Pickup truck dispatch for single heavy item transport across town.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Single Furniture Item Transport (Sofa / Bed / Fridge) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable local errands &amp; assistance services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Local Errands &amp; Assistance professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Single Furniture Item Transport (Sofa / Bed / Fridge) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.203053+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.203053+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Single Furniture Item Transport (Sofa / Bed / Fridge) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>d91c5724-7eb7-5f63-bb00-97461b843b2c</t>
+          <t>44bc15d3-2dc2-5407-9a0e-a84a536cf53d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance Service Variation 5</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Vehicle Assistance</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance</t>
+          <t>Car Battery Jump-Start &amp; Breakdown Assistance</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3000</v>
+        <v>499</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Emergency mechanic arrival with heavy jumper cables to jump-start dead car battery.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Car Battery Jump-Start &amp; Breakdown Assistance procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable local errands &amp; assistance services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Local Errands &amp; Assistance professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Car Battery Jump-Start &amp; Breakdown Assistance procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.205071+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.205071+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Car Battery Jump-Start &amp; Breakdown Assistance take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>d792920f-187c-5058-b2c9-35939008929f</t>
+          <t>1a248afa-46a2-5fa8-94fb-3acae99d76cd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vehicle Transport Service Variation 1</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Vehicle Assistance</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vehicle Transport</t>
+          <t>Intercity Vehicle Car / Bike Carrier Transport</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1400</v>
+        <v>5999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Enclosed car container or covered bike transport between major metro cities.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Intercity Vehicle Car / Bike Carrier Transport procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable vehicle transport services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Vehicle Transport professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Intercity Vehicle Car / Bike Carrier Transport procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.207315+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.207315+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does Intercity Vehicle Car / Bike Carrier Transport take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6466540c-1fd5-540f-b10f-e7feb984e053</t>
+          <t>ccd4d5ff-5b51-5c80-b1b7-7791fc2974c0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vehicle Transport Service Variation 2</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Vehicle Transport</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vehicle Transport</t>
+          <t>Vehicle Transport Premium Care Option 12</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1800</v>
+        <v>3199</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Vehicle Transport service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Vehicle Transport Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable vehicle transport services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Vehicle Transport professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Vehicle Transport Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.209636+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.209636+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Vehicle Transport Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ccd4d5ff-5b51-5c80-b1b7-7791fc2974c0</t>
+          <t>d792920f-187c-5058-b2c9-35939008929f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vehicle Transport Service Variation 3</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Vehicle Transport</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vehicle Transport</t>
+          <t>Vehicle Transport Premium Care Option 16</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2200</v>
+        <v>3599</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Vehicle Transport service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Vehicle Transport Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable vehicle transport services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Vehicle Transport professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Vehicle Transport Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.212779+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.212779+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Vehicle Transport Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1762,95 +1868,105 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vehicle Transport Service Variation 4</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Vehicle Transport</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vehicle Transport</t>
+          <t>Vehicle Transport Premium Care Option 19</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2600</v>
+        <v>3899</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Vehicle Transport service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Vehicle Transport Premium Care Option 19 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable vehicle transport services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Vehicle Transport professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Vehicle Transport Premium Care Option 19 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.214777+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.214777+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Vehicle Transport Premium Care Option 19 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1a248afa-46a2-5fa8-94fb-3acae99d76cd</t>
+          <t>6466540c-1fd5-540f-b10f-e7feb984e053</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vehicle Transport Service Variation 5</t>
+          <t>14. Moving, Delivery &amp; Local Assistance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14. Moving, Delivery &amp; Local Assistance</t>
+          <t>Vehicle Transport</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vehicle Transport</t>
+          <t>Vehicle Transport Premium Care Option 2</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3000</v>
+        <v>2199</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Vehicle Transport service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["Pre-move survey and planning", "Packing materials (basic)", "Loading, transport, and unloading", "Post-delivery clean-up"]</t>
+          <t>['Professional Vehicle Transport Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{"text": "Reliable vehicle transport services for a smooth and stress-free move.", "type": "description"}, {"type": "highlights", "items": ["Trained Vehicle Transport professionals", "GPS-tracked vehicles", "Fully insured service", "Damage-free guarantee"]}, {"type": "excluded_scope", "items": ["Cost of premium packing materials (bubble wrap, crates)", "Storage charges beyond 24 hours"]}, {"type": "process_steps", "steps": [{"title": "Pre-Move Survey", "description": "Assessing volume, fragile items, and special requirements", "step_number": 1}, {"title": "Packing", "description": "Carefully packing all items with appropriate materials", "step_number": 2}, {"title": "Loading &amp; Transport", "description": "Safely loading and transporting to the destination", "step_number": 3}, {"title": "Unloading &amp; Placement", "description": "Unloading and placing items as per customer instructions", "step_number": 4}, {"title": "Final Check &amp; Clean-Up", "description": "Verifying all items are delivered and removing packing waste", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Check all items against inventory within 24 hours", "Report any damage within 48 hours for warranty claim"]}, {"type": "tools_materials", "tools": ["Moving blankets and straps", "Trolleys and dollies", "Packing tape and boxes", "GPS-enabled truck"], "materials": []}, {"type": "customer_setup", "requirements": ["Sort and label boxes before the team arrives", "Disconnect appliances 24 hours before moving day", "Ensure parking access at both locations"]}, {"type": "expected_results", "items": "A damage-free, on-time move with all belongings safely delivered."}, {"type": "important_notes", "items": "Insurance coverage applies to standard household goods only; valuables should be declared upfront."}, {"type": "warranty", "details": "Free damage resolution within 48 hours of delivery if items are found damaged.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, basic packing materials are included; premium options are available at extra cost.", "question": "Do you provide packing materials?"}, {"answer": "Yes, all items are covered under transit insurance up to a declared value.", "question": "Are my belongings insured during transit?"}, {"answer": "Yes, our teams are equipped to move all types of furniture and appliances.", "question": "Can you move heavy or oversized furniture?"}, {"answer": "You will receive a live GPS tracking link once the vehicle departs.", "question": "How do I track my shipment?"}]}, {"type": "tips", "items": ["Label all boxes by room name to speed up unpacking."]}, {"dos": ["Declare high-value items before the move for proper insurance coverage."], "type": "dos_donts", "donts": ["Do not overload boxes — it increases the risk of damage."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Vehicle Transport Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.216816+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:34.216816+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Vehicle Transport Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>

--- a/backend/backups/category14_moving_delivery_local_assistance_FINAL.xlsx
+++ b/backend/backups/category14_moving_delivery_local_assistance_FINAL.xlsx
@@ -598,7 +598,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e216c0f0-cc0c-5dfb-ae9d-b71cc9ee5f06</t>
+          <t>bf9ef6d3-0143-5c64-9c1f-8463308554b7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -613,47 +613,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Premium Care Option 18</t>
+          <t>3 BHK Luxury Villa Inter-State Relocation</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3799</v>
+        <v>12999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Specialized high-end Home Shifting &amp; Packing service tailored to specific client needs with extended guarantee.</t>
+          <t>Heavy-duty wooden crating for chandeliers, TV packing, and dedicated container truck.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>['Professional Home Shifting &amp; Packing Premium Care Option 18 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional 3 BHK Luxury Villa Inter-State Relocation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>['Complete Home Shifting &amp; Packing Premium Care Option 18 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete 3 BHK Luxury Villa Inter-State Relocation procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Home Shifting &amp; Packing Premium Care Option 18 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 480 minutes.', 'question': 'How long does 3 BHK Luxury Villa Inter-State Relocation take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6dbabdc9-db64-5d81-bbdb-3e92e340fb58</t>
+          <t>e216c0f0-cc0c-5dfb-ae9d-b71cc9ee5f06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -668,47 +668,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Premium Care Option 3</t>
+          <t>Kitchen Crockery &amp; Fragile China Safe Packing</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2299</v>
+        <v>1499</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Specialized high-end Home Shifting &amp; Packing service tailored to specific client needs with extended guarantee.</t>
+          <t>Specialized honeycomb paper wrapping and double-walled boxes for fragile glassware.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>['Professional Home Shifting &amp; Packing Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Kitchen Crockery &amp; Fragile China Safe Packing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>['Complete Home Shifting &amp; Packing Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Kitchen Crockery &amp; Fragile China Safe Packing procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Home Shifting &amp; Packing Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Kitchen Crockery &amp; Fragile China Safe Packing take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bf9ef6d3-0143-5c64-9c1f-8463308554b7</t>
+          <t>6dbabdc9-db64-5d81-bbdb-3e92e340fb58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -723,40 +723,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Home Shifting &amp; Packing Premium Care Option 9</t>
+          <t>Studio / 1 RK Compact Shifting Service</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2899</v>
+        <v>3499</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Specialized high-end Home Shifting &amp; Packing service tailored to specific client needs with extended guarantee.</t>
+          <t>Fast shifting with 2 helpers, foam padding, and mini tempo transport.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>['Professional Home Shifting &amp; Packing Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Studio / 1 RK Compact Shifting Service procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>['Complete Home Shifting &amp; Packing Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Studio / 1 RK Compact Shifting Service procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Home Shifting &amp; Packing Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 180 minutes.', 'question': 'How long does Studio / 1 RK Compact Shifting Service take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -778,47 +778,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Premium Care Option 14</t>
+          <t>Complete Garage / Balcony Junk Clutter Hauling</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3399</v>
+        <v>1299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
+          <t>Clearing rusted pipes, obsolete boxes, paint cans, and thoroughly sweeping the area.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Complete Garage / Balcony Junk Clutter Hauling procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Complete Garage / Balcony Junk Clutter Hauling procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Complete Garage / Balcony Junk Clutter Hauling take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7d11b486-1097-5341-a8a5-87ba0f75c18b</t>
+          <t>82213c14-7b97-5dad-8721-f2d524f8fc70</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -833,47 +833,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Premium Care Option 4</t>
+          <t>E-Waste Eco-Friendly Recycling Pickup</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2399</v>
+        <v>499</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
+          <t>Doorstep collection of old CRT monitors, dead CPUs, wires, and printers for certified recycling.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional E-Waste Eco-Friendly Recycling Pickup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete E-Waste Eco-Friendly Recycling Pickup procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does E-Waste Eco-Friendly Recycling Pickup take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>82213c14-7b97-5dad-8721-f2d524f8fc70</t>
+          <t>ba26862d-85dd-5c2e-9ba0-78b615e06ad5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -888,47 +888,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Premium Care Option 5</t>
+          <t>Mattress &amp; Foam Scrap Disposal Service</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2499</v>
+        <v>699</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
+          <t>Heavy lifting and transport of bulky soiled mattresses for responsible disposal.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Mattress &amp; Foam Scrap Disposal Service procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Mattress &amp; Foam Scrap Disposal Service procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Mattress &amp; Foam Scrap Disposal Service take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9d2e0a0b-cae2-5e9e-864b-e9c4084176e4</t>
+          <t>7d11b486-1097-5341-a8a5-87ba0f75c18b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -943,47 +943,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Premium Care Option 6</t>
+          <t>Old Wooden Furniture Scrapping &amp; Disposal</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2599</v>
+        <v>999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
+          <t>Dismantling heavy broken beds, almirahs, and loading into municipal disposal trucks.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Old Wooden Furniture Scrapping &amp; Disposal procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Old Wooden Furniture Scrapping &amp; Disposal procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Old Wooden Furniture Scrapping &amp; Disposal take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ba26862d-85dd-5c2e-9ba0-78b615e06ad5</t>
+          <t>9d2e0a0b-cae2-5e9e-864b-e9c4084176e4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -998,47 +998,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Junk Removal &amp; Disposal Premium Care Option 8</t>
+          <t>Renovation Debris &amp; Rubble Masonry Clearance</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2799</v>
+        <v>1799</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Specialized high-end Junk Removal &amp; Disposal service tailored to specific client needs with extended guarantee.</t>
+          <t>Clearing cement sacks, plaster waste, and broken tiles into commercial tipper trucks.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>['Professional Junk Removal &amp; Disposal Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Renovation Debris &amp; Rubble Masonry Clearance procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>['Complete Junk Removal &amp; Disposal Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Renovation Debris &amp; Rubble Masonry Clearance procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Junk Removal &amp; Disposal Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Renovation Debris &amp; Rubble Masonry Clearance take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bfc1a8a7-8d4f-5c7d-8866-6f33a9a90c3d</t>
+          <t>c5096bf4-5677-50ed-bd66-23ab4e909013</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1053,47 +1053,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Premium Care Option 10</t>
+          <t>Fragile Bakery Cake &amp; Floral Gift Delivery</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2999</v>
+        <v>299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Specialized high-end Last-Mile Delivery service tailored to specific client needs with extended guarantee.</t>
+          <t>Air-conditioned car transport preventing birthday cake melting or bouquet damage.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>['Professional Last-Mile Delivery Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Fragile Bakery Cake &amp; Floral Gift Delivery procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>['Complete Last-Mile Delivery Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Fragile Bakery Cake &amp; Floral Gift Delivery procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Last-Mile Delivery Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Fragile Bakery Cake &amp; Floral Gift Delivery take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>c5096bf4-5677-50ed-bd66-23ab4e909013</t>
+          <t>d569432a-b4cd-5584-9b6b-4a617ee57c03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1108,40 +1108,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Premium Care Option 11</t>
+          <t>Heavy Hardware &amp; Appliance Inter-Store Transit</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3099</v>
+        <v>699</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Specialized high-end Last-Mile Delivery service tailored to specific client needs with extended guarantee.</t>
+          <t>Transporting air conditioners, tiles, or sanitaryware from wholesale mandi to site.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>['Professional Last-Mile Delivery Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Heavy Hardware &amp; Appliance Inter-Store Transit procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>['Complete Last-Mile Delivery Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Heavy Hardware &amp; Appliance Inter-Store Transit procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Last-Mile Delivery Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Heavy Hardware &amp; Appliance Inter-Store Transit take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1163,47 +1163,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Premium Care Option 13</t>
+          <t>Retail Store Same-Day Parcel Dispatch</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3299</v>
+        <v>399</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Specialized high-end Last-Mile Delivery service tailored to specific client needs with extended guarantee.</t>
+          <t>Batch pickup of ecommerce packages from local boutiques delivered to city customers.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>['Professional Last-Mile Delivery Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Retail Store Same-Day Parcel Dispatch procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>['Complete Last-Mile Delivery Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Retail Store Same-Day Parcel Dispatch procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Last-Mile Delivery Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Retail Store Same-Day Parcel Dispatch take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>d569432a-b4cd-5584-9b6b-4a617ee57c03</t>
+          <t>bfc1a8a7-8d4f-5c7d-8866-6f33a9a90c3d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1218,47 +1218,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Last-Mile Delivery Premium Care Option 15</t>
+          <t>Two-Hour Express City Document Delivery</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3499</v>
+        <v>199</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Specialized high-end Last-Mile Delivery service tailored to specific client needs with extended guarantee.</t>
+          <t>Urgent passport, signed agreement, or invoice courier with live GPS tracking.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>['Professional Last-Mile Delivery Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Two-Hour Express City Document Delivery procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>['Complete Last-Mile Delivery Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Two-Hour Express City Document Delivery procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Last-Mile Delivery Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Two-Hour Express City Document Delivery take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>46d8db20-3e81-5240-8af7-c6aeb1680155</t>
+          <t>a698a0c1-edb5-5247-92b7-7afd5d00c0d7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1273,40 +1273,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance Premium Care Option 1</t>
+          <t>Gift Wrapping &amp; Festive Hamper Assembly Runner</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2099</v>
+        <v>599</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Specialized high-end Local Errands &amp; Assistance service tailored to specific client needs with extended guarantee.</t>
+          <t>Procuring gift ribbons, wrapping boxes, and delivering Diwali/Christmas hampers.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>['Professional Local Errands &amp; Assistance Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Gift Wrapping &amp; Festive Hamper Assembly Runner procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>['Complete Local Errands &amp; Assistance Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Gift Wrapping &amp; Festive Hamper Assembly Runner procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Local Errands &amp; Assistance Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Gift Wrapping &amp; Festive Hamper Assembly Runner take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1328,47 +1328,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance Premium Care Option 17</t>
+          <t>Key Duplicate Making &amp; Locksmith Doorstep Pickup</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3699</v>
+        <v>349</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Specialized high-end Local Errands &amp; Assistance service tailored to specific client needs with extended guarantee.</t>
+          <t>Collecting master key, getting computer duplicate cut at market, and returning to home.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>['Professional Local Errands &amp; Assistance Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Key Duplicate Making &amp; Locksmith Doorstep Pickup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>['Complete Local Errands &amp; Assistance Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Key Duplicate Making &amp; Locksmith Doorstep Pickup procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Local Errands &amp; Assistance Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 30 minutes.', 'question': 'How long does Key Duplicate Making &amp; Locksmith Doorstep Pickup take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a698a0c1-edb5-5247-92b7-7afd5d00c0d7</t>
+          <t>46d8db20-3e81-5240-8af7-c6aeb1680155</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1383,40 +1383,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Local Errands &amp; Assistance Premium Care Option 7</t>
+          <t>Standing in Long Queue Assistant (RTO/Consulate)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2699</v>
+        <v>499</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Specialized high-end Local Errands &amp; Assistance service tailored to specific client needs with extended guarantee.</t>
+          <t>Helper standing in line on your behalf at government offices or visa centers.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>['Professional Local Errands &amp; Assistance Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Standing in Long Queue Assistant (RTO/Consulate) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>['Complete Local Errands &amp; Assistance Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Standing in Long Queue Assistant (RTO/Consulate) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Local Errands &amp; Assistance Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Standing in Long Queue Assistant (RTO/Consulate) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ccd4d5ff-5b51-5c80-b1b7-7791fc2974c0</t>
+          <t>f7feff42-4eec-5316-a9c3-98e2f4088c57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1768,47 +1768,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vehicle Transport Premium Care Option 12</t>
+          <t>Airport Chauffeur Driven Car Drop &amp; Valet Return</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3199</v>
+        <v>999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Specialized high-end Vehicle Transport service tailored to specific client needs with extended guarantee.</t>
+          <t>Driver dropping you at airport terminal and safely parking car back at your residence.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>['Professional Vehicle Transport Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Airport Chauffeur Driven Car Drop &amp; Valet Return procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>['Complete Vehicle Transport Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Airport Chauffeur Driven Car Drop &amp; Valet Return procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Vehicle Transport Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Airport Chauffeur Driven Car Drop &amp; Valet Return take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>d792920f-187c-5058-b2c9-35939008929f</t>
+          <t>ccd4d5ff-5b51-5c80-b1b7-7791fc2974c0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1823,47 +1823,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vehicle Transport Premium Care Option 16</t>
+          <t>Flatbed Hydraulic Tow Truck for Premium Cars</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3599</v>
+        <v>1899</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Specialized high-end Vehicle Transport service tailored to specific client needs with extended guarantee.</t>
+          <t>Zero-ground clearance flatbed towing for luxury sedans and automatic SUVs.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>['Professional Vehicle Transport Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Flatbed Hydraulic Tow Truck for Premium Cars procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>['Complete Vehicle Transport Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Flatbed Hydraulic Tow Truck for Premium Cars procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Vehicle Transport Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Flatbed Hydraulic Tow Truck for Premium Cars take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f7feff42-4eec-5316-a9c3-98e2f4088c57</t>
+          <t>d792920f-187c-5058-b2c9-35939008929f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1878,40 +1878,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vehicle Transport Premium Care Option 19</t>
+          <t>Interstate Bike Relocation with Bubble Wrap</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3899</v>
+        <v>3499</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Specialized high-end Vehicle Transport service tailored to specific client needs with extended guarantee.</t>
+          <t>Full motorcycle bubble wrapping, petrol draining, and train/truck container loading.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>['Professional Vehicle Transport Premium Care Option 19 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Interstate Bike Relocation with Bubble Wrap procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>['Complete Vehicle Transport Premium Care Option 19 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Interstate Bike Relocation with Bubble Wrap procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Vehicle Transport Premium Care Option 19 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Interstate Bike Relocation with Bubble Wrap take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1933,40 +1933,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vehicle Transport Premium Care Option 2</t>
+          <t>Two-Wheeler Covered City Bike Towing</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2199</v>
+        <v>899</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Specialized high-end Vehicle Transport service tailored to specific client needs with extended guarantee.</t>
+          <t>Hydraulic ramp pickup truck for punctured, stalled, or accidental motorcycles.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>['Professional Vehicle Transport Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Two-Wheeler Covered City Bike Towing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>['Complete Vehicle Transport Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Two-Wheeler Covered City Bike Towing procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Vehicle Transport Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Two-Wheeler Covered City Bike Towing take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
